--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/ARKANSAS_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/ARKANSAS_2017.xlsx
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C120">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C199">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C518">
